--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1229-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1229-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEBF6FF5-311D-4198-935A-D323D0017DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA174A22-FB0E-4DB6-9424-2C3995F958B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{18C2DE9D-21CF-48E4-B064-538691470321}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A8298800-3BFF-48F4-AD74-7997500B4072}"/>
   </bookViews>
   <sheets>
     <sheet name="1229-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1658,30 +1658,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15F17DF9-6522-46E5-8908-E424C1024177}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15612CC7-E190-45F9-99DD-831D4F99332D}">
   <dimension ref="A1:X74"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -1715,7 +1715,7 @@
       <c r="W1" s="35"/>
       <c r="X1" s="27"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
@@ -1751,7 +1751,7 @@
       <c r="W2" s="37"/>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>2</v>
       </c>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="X3" s="41"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="30"/>
       <c r="B4" s="31"/>
       <c r="C4" s="7"/>
@@ -1871,7 +1871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="42">
         <v>2025</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="44">
         <v>2024</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="42">
         <v>2023</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="44">
         <v>2022</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="46">
         <v>2021</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="48"/>
       <c r="B26" s="49"/>
       <c r="C26" s="20" t="s">
@@ -3443,7 +3443,7 @@
       <c r="W26" s="55"/>
       <c r="X26" s="51"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="52" t="s">
         <v>29</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="53"/>
       <c r="B28" s="53"/>
       <c r="C28" s="22" t="s">
@@ -3545,7 +3545,7 @@
       <c r="W28" s="55"/>
       <c r="X28" s="51"/>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="58">
         <v>2020</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="60"/>
       <c r="B33" s="61"/>
       <c r="C33" s="24" t="s">
@@ -3867,7 +3867,7 @@
       <c r="W33" s="67"/>
       <c r="X33" s="63"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="42">
         <v>2019</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="44">
         <v>2018</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="42">
         <v>2017</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="44">
         <v>2016</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="42">
         <v>2015</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="44">
         <v>2014</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="42">
         <v>2013</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="44">
         <v>2012</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="42">
         <v>2011</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="44">
         <v>2010</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="42">
         <v>2009</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="44">
         <v>2008</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="42">
         <v>2007</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="44">
         <v>2006</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="42">
         <v>2005</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>7.24</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="44">
         <v>2004</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="42">
         <v>2003</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="44">
         <v>2002</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="42">
         <v>2001</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="44">
         <v>2000</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="42">
         <v>1999</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="44">
         <v>1998</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="42">
         <v>1997</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="44">
         <v>1996</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="42">
         <v>1995</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="44">
         <v>1994</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="42">
         <v>1993</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="58">
         <v>1992</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="60"/>
       <c r="B62" s="61"/>
       <c r="C62" s="24" t="s">
@@ -5911,7 +5911,7 @@
       <c r="W62" s="67"/>
       <c r="X62" s="63"/>
     </row>
-    <row r="63" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="42">
         <v>1991</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="58">
         <v>1990</v>
       </c>
@@ -6055,7 +6055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="60"/>
       <c r="B65" s="61"/>
       <c r="C65" s="24" t="s">
@@ -6083,7 +6083,7 @@
       <c r="W65" s="67"/>
       <c r="X65" s="63"/>
     </row>
-    <row r="66" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="46">
         <v>1989</v>
       </c>
@@ -6155,7 +6155,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="48"/>
       <c r="B67" s="49"/>
       <c r="C67" s="20" t="s">
@@ -6183,7 +6183,7 @@
       <c r="W67" s="55"/>
       <c r="X67" s="51"/>
     </row>
-    <row r="68" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="44">
         <v>1988</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="42">
         <v>1987</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="44">
         <v>1986</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="42">
         <v>1985</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="44">
         <v>1984</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="42">
         <v>1983</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="44" t="s">
         <v>78</v>
       </c>
